--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348673</v>
+        <v>120348702</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552674</v>
+        <v>552808</v>
       </c>
       <c r="R3" t="n">
-        <v>7016868</v>
+        <v>7016822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348671</v>
+        <v>120348675</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552779</v>
+        <v>552701</v>
       </c>
       <c r="R4" t="n">
-        <v>7016821</v>
+        <v>7016860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348702</v>
+        <v>120348673</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552808</v>
+        <v>552674</v>
       </c>
       <c r="R5" t="n">
-        <v>7016822</v>
+        <v>7016868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348675</v>
+        <v>120348671</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552701</v>
+        <v>552779</v>
       </c>
       <c r="R6" t="n">
-        <v>7016860</v>
+        <v>7016821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348672</v>
+        <v>120348702</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552734</v>
+        <v>552808</v>
       </c>
       <c r="R2" t="n">
-        <v>7016864</v>
+        <v>7016822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348702</v>
+        <v>120348672</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552808</v>
+        <v>552734</v>
       </c>
       <c r="R3" t="n">
-        <v>7016822</v>
+        <v>7016864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348675</v>
+        <v>120348673</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552701</v>
+        <v>552674</v>
       </c>
       <c r="R4" t="n">
-        <v>7016860</v>
+        <v>7016868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348673</v>
+        <v>120348675</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552674</v>
+        <v>552701</v>
       </c>
       <c r="R5" t="n">
-        <v>7016868</v>
+        <v>7016860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348672</v>
+        <v>120348675</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552734</v>
+        <v>552701</v>
       </c>
       <c r="R3" t="n">
-        <v>7016864</v>
+        <v>7016860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348673</v>
+        <v>120348671</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552674</v>
+        <v>552779</v>
       </c>
       <c r="R4" t="n">
-        <v>7016868</v>
+        <v>7016821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348675</v>
+        <v>120348672</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552701</v>
+        <v>552734</v>
       </c>
       <c r="R5" t="n">
-        <v>7016860</v>
+        <v>7016864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348671</v>
+        <v>120348673</v>
       </c>
       <c r="B6" t="n">
-        <v>90742</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552779</v>
+        <v>552674</v>
       </c>
       <c r="R6" t="n">
-        <v>7016821</v>
+        <v>7016868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348702</v>
+        <v>120348672</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552808</v>
+        <v>552734</v>
       </c>
       <c r="R2" t="n">
-        <v>7016822</v>
+        <v>7016864</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348675</v>
+        <v>120348702</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552701</v>
+        <v>552808</v>
       </c>
       <c r="R3" t="n">
-        <v>7016860</v>
+        <v>7016822</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348671</v>
+        <v>120348673</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552779</v>
+        <v>552674</v>
       </c>
       <c r="R4" t="n">
-        <v>7016821</v>
+        <v>7016868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348672</v>
+        <v>120348675</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552734</v>
+        <v>552701</v>
       </c>
       <c r="R5" t="n">
-        <v>7016864</v>
+        <v>7016860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348673</v>
+        <v>120348671</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552674</v>
+        <v>552779</v>
       </c>
       <c r="R6" t="n">
-        <v>7016868</v>
+        <v>7016821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348672</v>
+        <v>120348702</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552734</v>
+        <v>552808</v>
       </c>
       <c r="R2" t="n">
-        <v>7016864</v>
+        <v>7016822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348702</v>
+        <v>120348673</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552808</v>
+        <v>552674</v>
       </c>
       <c r="R3" t="n">
-        <v>7016822</v>
+        <v>7016868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348673</v>
+        <v>120348672</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552674</v>
+        <v>552734</v>
       </c>
       <c r="R4" t="n">
-        <v>7016868</v>
+        <v>7016864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348702</v>
+        <v>120348675</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552808</v>
+        <v>552701</v>
       </c>
       <c r="R2" t="n">
-        <v>7016822</v>
+        <v>7016860</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348673</v>
+        <v>120348672</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552674</v>
+        <v>552734</v>
       </c>
       <c r="R3" t="n">
-        <v>7016868</v>
+        <v>7016864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348672</v>
+        <v>120348671</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552734</v>
+        <v>552779</v>
       </c>
       <c r="R4" t="n">
-        <v>7016864</v>
+        <v>7016821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348675</v>
+        <v>120348702</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552701</v>
+        <v>552808</v>
       </c>
       <c r="R5" t="n">
-        <v>7016860</v>
+        <v>7016822</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348671</v>
+        <v>120348673</v>
       </c>
       <c r="B6" t="n">
-        <v>90742</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552779</v>
+        <v>552674</v>
       </c>
       <c r="R6" t="n">
-        <v>7016821</v>
+        <v>7016868</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348675</v>
+        <v>120348702</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552701</v>
+        <v>552808</v>
       </c>
       <c r="R2" t="n">
-        <v>7016860</v>
+        <v>7016822</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348672</v>
+        <v>120348671</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552734</v>
+        <v>552779</v>
       </c>
       <c r="R3" t="n">
-        <v>7016864</v>
+        <v>7016821</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348671</v>
+        <v>120348672</v>
       </c>
       <c r="B4" t="n">
-        <v>90742</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552779</v>
+        <v>552734</v>
       </c>
       <c r="R4" t="n">
-        <v>7016821</v>
+        <v>7016864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348702</v>
+        <v>120348673</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552808</v>
+        <v>552674</v>
       </c>
       <c r="R5" t="n">
-        <v>7016822</v>
+        <v>7016868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348673</v>
+        <v>120348675</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552674</v>
+        <v>552701</v>
       </c>
       <c r="R6" t="n">
-        <v>7016868</v>
+        <v>7016860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348671</v>
+        <v>103401971</v>
       </c>
       <c r="B2" t="n">
-        <v>90804</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höksberget, Jmt</t>
+          <t>Slankmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552779</v>
+        <v>552751</v>
       </c>
       <c r="R2" t="n">
-        <v>7016821</v>
+        <v>7016730</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,12 +775,7 @@
         <v>120348672</v>
       </c>
       <c r="B3" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348675</v>
+        <v>120348671</v>
       </c>
       <c r="B4" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552701</v>
+        <v>552779</v>
       </c>
       <c r="R4" t="n">
-        <v>7016860</v>
+        <v>7016821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,12 +969,7 @@
         <v>120348673</v>
       </c>
       <c r="B5" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348702</v>
+        <v>120348675</v>
       </c>
       <c r="B6" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552808</v>
+        <v>552701</v>
       </c>
       <c r="R6" t="n">
-        <v>7016822</v>
+        <v>7016860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 30465-2024 artfynd.xlsx
+++ b/artfynd/A 30465-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401971</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348671</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348673</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,8 +1192,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>